--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:06:15+00:00</t>
+    <t>2024-05-16T08:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T13:41:42+00:00</t>
+    <t>2025-02-27T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T09:48:09+00:00</t>
+    <t>2025-03-04T08:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:17:54+00:00</t>
+    <t>2025-03-06T14:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:47:34+00:00</t>
+    <t>2025-03-07T13:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:06:03+00:00</t>
+    <t>2025-04-23T14:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T14:15:06+00:00</t>
+    <t>2025-05-21T14:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:16+00:00</t>
+    <t>2025-07-21T12:31:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:31:31+00:00</t>
+    <t>2025-10-13T07:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:09+00:00</t>
+    <t>2025-10-13T07:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:03+00:00</t>
+    <t>2026-01-29T14:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -76,7 +76,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -76,7 +76,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-method-glucose-vs.xlsx
+++ b/main/ig/ValueSet-method-glucose-vs.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
